--- a/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
+++ b/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
@@ -1170,28 +1170,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1500</v>
+        <v>1616</v>
       </c>
       <c r="C14" t="n">
-        <v>1674</v>
+        <v>1755</v>
       </c>
       <c r="D14" t="n">
-        <v>1500</v>
+        <v>1616</v>
       </c>
       <c r="E14" t="n">
-        <v>1674</v>
+        <v>1755</v>
       </c>
       <c r="F14" t="n">
-        <v>1500</v>
+        <v>1623</v>
       </c>
       <c r="G14" t="n">
-        <v>1674</v>
+        <v>1771</v>
       </c>
       <c r="H14" t="n">
-        <v>1500</v>
+        <v>1623</v>
       </c>
       <c r="I14" t="n">
-        <v>1674</v>
+        <v>1771</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2096,7 +2096,7 @@
         <v>0.0888888888888888</v>
       </c>
       <c r="P31" t="n">
-        <v>0.02</v>
+        <v>0.0888888888888888</v>
       </c>
     </row>
     <row r="32">
@@ -3614,13 +3614,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="C61" t="n">
         <v>150</v>
       </c>
       <c r="D61" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E61" t="n">
         <v>150</v>
@@ -3773,13 +3773,13 @@
         <v>873</v>
       </c>
       <c r="C64" t="n">
-        <v>1440</v>
+        <v>1337</v>
       </c>
       <c r="D64" t="n">
         <v>873</v>
       </c>
       <c r="E64" t="n">
-        <v>1440</v>
+        <v>1337</v>
       </c>
       <c r="F64" t="n">
         <v>863</v>
@@ -4394,28 +4394,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1080</v>
+        <v>1260</v>
       </c>
       <c r="C76" t="n">
-        <v>1153</v>
+        <v>1353</v>
       </c>
       <c r="D76" t="n">
-        <v>1080</v>
+        <v>1280</v>
       </c>
       <c r="E76" t="n">
-        <v>1153</v>
+        <v>1241</v>
       </c>
       <c r="F76" t="n">
-        <v>1080</v>
+        <v>1220</v>
       </c>
       <c r="G76" t="n">
-        <v>1153</v>
+        <v>1134</v>
       </c>
       <c r="H76" t="n">
-        <v>1080</v>
+        <v>1245</v>
       </c>
       <c r="I76" t="n">
-        <v>1153</v>
+        <v>1094</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
@@ -4657,25 +4657,25 @@
         <v>440</v>
       </c>
       <c r="C81" t="n">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="D81" t="n">
         <v>440</v>
       </c>
       <c r="E81" t="n">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="F81" t="n">
         <v>440</v>
       </c>
       <c r="G81" t="n">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="H81" t="n">
         <v>440</v>
       </c>
       <c r="I81" t="n">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
@@ -5333,25 +5333,25 @@
         <v>2024</v>
       </c>
       <c r="C94" t="n">
-        <v>1820</v>
+        <v>1843</v>
       </c>
       <c r="D94" t="n">
         <v>2024</v>
       </c>
       <c r="E94" t="n">
-        <v>1820</v>
+        <v>1843</v>
       </c>
       <c r="F94" t="n">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="G94" t="n">
-        <v>1820</v>
+        <v>1826</v>
       </c>
       <c r="H94" t="n">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="I94" t="n">
-        <v>1820</v>
+        <v>1826</v>
       </c>
       <c r="J94" t="b">
         <v>0</v>
@@ -6310,28 +6310,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1500</v>
+        <v>1616</v>
       </c>
       <c r="C14" t="n">
-        <v>1674</v>
+        <v>1755</v>
       </c>
       <c r="D14" t="n">
-        <v>1500</v>
+        <v>1616</v>
       </c>
       <c r="E14" t="n">
-        <v>1674</v>
+        <v>1755</v>
       </c>
       <c r="F14" t="n">
-        <v>1500</v>
+        <v>1623</v>
       </c>
       <c r="G14" t="n">
-        <v>1674</v>
+        <v>1771</v>
       </c>
       <c r="H14" t="n">
-        <v>1500</v>
+        <v>1623</v>
       </c>
       <c r="I14" t="n">
-        <v>1674</v>
+        <v>1771</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -6842,13 +6842,13 @@
         <v>620</v>
       </c>
       <c r="F24" t="n">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="G24" t="n">
         <v>620</v>
       </c>
       <c r="H24" t="n">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="I24" t="n">
         <v>620</v>
@@ -7337,10 +7337,10 @@
         <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>0.02</v>
+        <v>0.0888888888888888</v>
       </c>
       <c r="P33" t="n">
-        <v>0.02</v>
+        <v>0.0888888888888888</v>
       </c>
     </row>
     <row r="34">
@@ -7392,7 +7392,7 @@
         <v>0.0888888888888888</v>
       </c>
       <c r="P34" t="n">
-        <v>0.02</v>
+        <v>0.0888888888888888</v>
       </c>
     </row>
     <row r="35">
@@ -8962,13 +8962,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="C65" t="n">
         <v>150</v>
       </c>
       <c r="D65" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E65" t="n">
         <v>150</v>
@@ -9121,13 +9121,13 @@
         <v>873</v>
       </c>
       <c r="C68" t="n">
-        <v>1440</v>
+        <v>1337</v>
       </c>
       <c r="D68" t="n">
         <v>873</v>
       </c>
       <c r="E68" t="n">
-        <v>1440</v>
+        <v>1337</v>
       </c>
       <c r="F68" t="n">
         <v>863</v>
@@ -9846,28 +9846,28 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1080</v>
+        <v>1260</v>
       </c>
       <c r="C82" t="n">
-        <v>1153</v>
+        <v>1353</v>
       </c>
       <c r="D82" t="n">
-        <v>1080</v>
+        <v>1280</v>
       </c>
       <c r="E82" t="n">
-        <v>1153</v>
+        <v>1241</v>
       </c>
       <c r="F82" t="n">
-        <v>1080</v>
+        <v>1220</v>
       </c>
       <c r="G82" t="n">
-        <v>1153</v>
+        <v>1134</v>
       </c>
       <c r="H82" t="n">
-        <v>1080</v>
+        <v>1245</v>
       </c>
       <c r="I82" t="n">
-        <v>1153</v>
+        <v>1094</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
@@ -10109,25 +10109,25 @@
         <v>440</v>
       </c>
       <c r="C87" t="n">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="D87" t="n">
         <v>440</v>
       </c>
       <c r="E87" t="n">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="F87" t="n">
         <v>440</v>
       </c>
       <c r="G87" t="n">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="H87" t="n">
         <v>440</v>
       </c>
       <c r="I87" t="n">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
@@ -10785,25 +10785,25 @@
         <v>2024</v>
       </c>
       <c r="C100" t="n">
-        <v>1820</v>
+        <v>1843</v>
       </c>
       <c r="D100" t="n">
         <v>2024</v>
       </c>
       <c r="E100" t="n">
-        <v>1820</v>
+        <v>1843</v>
       </c>
       <c r="F100" t="n">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="G100" t="n">
-        <v>1820</v>
+        <v>1826</v>
       </c>
       <c r="H100" t="n">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="I100" t="n">
-        <v>1820</v>
+        <v>1826</v>
       </c>
       <c r="J100" t="b">
         <v>0</v>

--- a/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
+++ b/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
@@ -510,12 +510,12 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>HVDC_Direct</t>
+          <t>HVDC_MW_direct</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>HVDC_Indirect</t>
+          <t>HVDC_MW_Indirect</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -530,12 +530,12 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>HVDC_For_Direct</t>
+          <t>HVDC_FO_Rate_direct</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>HVDC_For_Indirect</t>
+          <t>HVDC_FO_Rate_indirect</t>
         </is>
       </c>
     </row>
@@ -5650,12 +5650,12 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>HVDC_Direct</t>
+          <t>HVDC_MW_direct</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>HVDC_Indirect</t>
+          <t>HVDC_MW_Indirect</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>HVDC_For_Direct</t>
+          <t>HVDC_FO_Rate_direct</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>HVDC_For_Indirect</t>
+          <t>HVDC_FO_Rate_indirect</t>
         </is>
       </c>
     </row>

--- a/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
+++ b/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
@@ -5525,7 +5525,7 @@
         <v>2</v>
       </c>
       <c r="O97" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="P97" t="n">
         <v>0.01</v>
@@ -10977,7 +10977,7 @@
         <v>2</v>
       </c>
       <c r="O103" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="P103" t="n">
         <v>0.01</v>

--- a/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
+++ b/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1894,32 +1894,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CZ-PL</t>
+          <t>CZ-SK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1050</v>
+        <v>1700</v>
       </c>
       <c r="C28" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="D28" t="n">
-        <v>1050</v>
+        <v>1700</v>
       </c>
       <c r="E28" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="F28" t="n">
-        <v>1050</v>
+        <v>1700</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="H28" t="n">
-        <v>1050</v>
+        <v>1700</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -1946,32 +1946,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CZ-SK</t>
+          <t>DE-DEkf</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1700</v>
+        <v>400</v>
       </c>
       <c r="C29" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="D29" t="n">
-        <v>1700</v>
+        <v>400</v>
       </c>
       <c r="E29" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="F29" t="n">
-        <v>1700</v>
+        <v>400</v>
       </c>
       <c r="G29" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="H29" t="n">
-        <v>1700</v>
+        <v>400</v>
       </c>
       <c r="I29" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -1998,136 +1998,136 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DE-DEkf</t>
+          <t>DE-DKe</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>400</v>
+        <v>585</v>
       </c>
       <c r="C30" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="D30" t="n">
-        <v>400</v>
+        <v>585</v>
       </c>
       <c r="E30" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F30" t="n">
-        <v>400</v>
+        <v>585</v>
       </c>
       <c r="G30" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="H30" t="n">
-        <v>400</v>
+        <v>585</v>
       </c>
       <c r="I30" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>0.0888888888888888</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>0.0888888888888888</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DE-DKe</t>
+          <t>DE-DKw</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>585</v>
+        <v>3500</v>
       </c>
       <c r="C31" t="n">
-        <v>600</v>
+        <v>3500</v>
       </c>
       <c r="D31" t="n">
-        <v>585</v>
+        <v>3500</v>
       </c>
       <c r="E31" t="n">
-        <v>600</v>
+        <v>3500</v>
       </c>
       <c r="F31" t="n">
-        <v>585</v>
+        <v>3500</v>
       </c>
       <c r="G31" t="n">
-        <v>600</v>
+        <v>3500</v>
       </c>
       <c r="H31" t="n">
-        <v>585</v>
+        <v>3500</v>
       </c>
       <c r="I31" t="n">
-        <v>600</v>
+        <v>3500</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>585</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0888888888888888</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0888888888888888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DE-DKw</t>
+          <t>DE-FR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="C32" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="D32" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="E32" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="F32" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="G32" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="H32" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="I32" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -2154,32 +2154,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DE-FR</t>
+          <t>DE-LU</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="C33" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="D33" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="E33" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="F33" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="G33" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="H33" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="I33" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -2206,32 +2206,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DE-LU</t>
+          <t>DE-NL</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="C34" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="D34" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="E34" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="F34" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="G34" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="H34" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="I34" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
@@ -2258,99 +2258,99 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DE-NL</t>
+          <t>DE-NOs</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="C35" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="D35" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="E35" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="F35" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="G35" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="H35" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="I35" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DE-NOs</t>
+          <t>DE-SE4</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="C36" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="D36" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="E36" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="F36" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="G36" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="H36" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="I36" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="L36" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
         <v>0.02</v>
@@ -2362,145 +2362,145 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DE-PL</t>
+          <t>DE-UKgb</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="C37" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="D37" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="E37" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="F37" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="G37" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="H37" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="I37" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DE-SE4</t>
+          <t>DEkf-DKkf</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="C38" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="D38" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="E38" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="F38" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="G38" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="H38" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="I38" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DE-UKgb</t>
+          <t>DKe-DKkf</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="C39" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="D39" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="E39" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="F39" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="G39" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="H39" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="I39" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="L39" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="M39" t="n">
         <v>2</v>
@@ -2509,108 +2509,108 @@
         <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DEkf-DKkf</t>
+          <t>DKe-DKw</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C40" t="n">
-        <v>400</v>
+        <v>590</v>
       </c>
       <c r="D40" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E40" t="n">
-        <v>400</v>
+        <v>590</v>
       </c>
       <c r="F40" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G40" t="n">
-        <v>400</v>
+        <v>590</v>
       </c>
       <c r="H40" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I40" t="n">
-        <v>400</v>
+        <v>590</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>0.0888888888888888</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>0.0888888888888888</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DKe-DKkf</t>
+          <t>DKe-SE4</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>600</v>
+        <v>1700</v>
       </c>
       <c r="C41" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="D41" t="n">
-        <v>600</v>
+        <v>1700</v>
       </c>
       <c r="E41" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="F41" t="n">
-        <v>600</v>
+        <v>1267</v>
       </c>
       <c r="G41" t="n">
-        <v>600</v>
+        <v>867</v>
       </c>
       <c r="H41" t="n">
-        <v>600</v>
+        <v>1267</v>
       </c>
       <c r="I41" t="n">
-        <v>600</v>
+        <v>867</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -2622,41 +2622,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DKe-DKw</t>
+          <t>DKw-NL</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="C42" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="D42" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E42" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="F42" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G42" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="H42" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I42" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L42" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
@@ -2674,99 +2674,99 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DKe-SE4</t>
+          <t>DKw-NOs</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1700</v>
+        <v>1632</v>
       </c>
       <c r="C43" t="n">
-        <v>1300</v>
+        <v>1632</v>
       </c>
       <c r="D43" t="n">
-        <v>1700</v>
+        <v>1632</v>
       </c>
       <c r="E43" t="n">
-        <v>1300</v>
+        <v>1632</v>
       </c>
       <c r="F43" t="n">
-        <v>1267</v>
+        <v>1632</v>
       </c>
       <c r="G43" t="n">
-        <v>867</v>
+        <v>1632</v>
       </c>
       <c r="H43" t="n">
-        <v>1267</v>
+        <v>1632</v>
       </c>
       <c r="I43" t="n">
-        <v>867</v>
+        <v>1632</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1632</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1632</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>0.0888888888888888</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>0.0888888888888888</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DKw-NL</t>
+          <t>DKw-SE3</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="C44" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="D44" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="E44" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="F44" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="G44" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="H44" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="I44" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="L44" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
         <v>0.0888888888888888</v>
@@ -2778,47 +2778,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DKw-NOs</t>
+          <t>DKw-UKgb</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="C45" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="D45" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="E45" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="F45" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="G45" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="H45" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="I45" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="L45" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
         <v>0.0888888888888888</v>
@@ -2830,41 +2830,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DKw-SE3</t>
+          <t>EE-FI</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>715</v>
+        <v>1016</v>
       </c>
       <c r="C46" t="n">
-        <v>715</v>
+        <v>1016</v>
       </c>
       <c r="D46" t="n">
-        <v>715</v>
+        <v>1016</v>
       </c>
       <c r="E46" t="n">
-        <v>715</v>
+        <v>1016</v>
       </c>
       <c r="F46" t="n">
-        <v>715</v>
+        <v>1016</v>
       </c>
       <c r="G46" t="n">
-        <v>715</v>
+        <v>1016</v>
       </c>
       <c r="H46" t="n">
-        <v>715</v>
+        <v>1016</v>
       </c>
       <c r="I46" t="n">
-        <v>715</v>
+        <v>1016</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>715</v>
+        <v>1016</v>
       </c>
       <c r="L46" t="n">
-        <v>715</v>
+        <v>1016</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
@@ -2873,145 +2873,145 @@
         <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.11</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DKw-UKgb</t>
+          <t>EE-LV</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1400</v>
+        <v>1035</v>
       </c>
       <c r="C47" t="n">
-        <v>1400</v>
+        <v>845</v>
       </c>
       <c r="D47" t="n">
-        <v>1400</v>
+        <v>1035</v>
       </c>
       <c r="E47" t="n">
-        <v>1400</v>
+        <v>845</v>
       </c>
       <c r="F47" t="n">
-        <v>1400</v>
+        <v>780</v>
       </c>
       <c r="G47" t="n">
-        <v>1400</v>
+        <v>845</v>
       </c>
       <c r="H47" t="n">
-        <v>1400</v>
+        <v>780</v>
       </c>
       <c r="I47" t="n">
-        <v>1400</v>
+        <v>845</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0888888888888888</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0888888888888888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EE-FI</t>
+          <t>ES-FR</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1016</v>
+        <v>5400</v>
       </c>
       <c r="C48" t="n">
-        <v>1016</v>
+        <v>5300</v>
       </c>
       <c r="D48" t="n">
-        <v>1016</v>
+        <v>5600</v>
       </c>
       <c r="E48" t="n">
-        <v>1016</v>
+        <v>5300</v>
       </c>
       <c r="F48" t="n">
-        <v>1016</v>
+        <v>3600</v>
       </c>
       <c r="G48" t="n">
-        <v>1016</v>
+        <v>5300</v>
       </c>
       <c r="H48" t="n">
-        <v>1016</v>
+        <v>5500</v>
       </c>
       <c r="I48" t="n">
-        <v>1016</v>
+        <v>5100</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1016</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1016</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EE-LV</t>
+          <t>ES-PT</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1035</v>
+        <v>4200</v>
       </c>
       <c r="C49" t="n">
-        <v>845</v>
+        <v>3500</v>
       </c>
       <c r="D49" t="n">
-        <v>1035</v>
+        <v>4200</v>
       </c>
       <c r="E49" t="n">
-        <v>845</v>
+        <v>3500</v>
       </c>
       <c r="F49" t="n">
-        <v>780</v>
+        <v>4200</v>
       </c>
       <c r="G49" t="n">
-        <v>845</v>
+        <v>3500</v>
       </c>
       <c r="H49" t="n">
-        <v>780</v>
+        <v>4200</v>
       </c>
       <c r="I49" t="n">
-        <v>845</v>
+        <v>3500</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
@@ -3038,32 +3038,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ES-FR</t>
+          <t>FI-NOn</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5400</v>
+        <v>80</v>
       </c>
       <c r="C50" t="n">
-        <v>5300</v>
+        <v>80</v>
       </c>
       <c r="D50" t="n">
-        <v>5600</v>
+        <v>80</v>
       </c>
       <c r="E50" t="n">
-        <v>5300</v>
+        <v>80</v>
       </c>
       <c r="F50" t="n">
-        <v>3600</v>
+        <v>80</v>
       </c>
       <c r="G50" t="n">
-        <v>5300</v>
+        <v>80</v>
       </c>
       <c r="H50" t="n">
-        <v>5500</v>
+        <v>80</v>
       </c>
       <c r="I50" t="n">
-        <v>5100</v>
+        <v>80</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
@@ -3090,32 +3090,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ES-PT</t>
+          <t>FI-SE1</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="C51" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="D51" t="n">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="E51" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="F51" t="n">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="G51" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="H51" t="n">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="I51" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
@@ -3142,99 +3142,99 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FI-NOn</t>
+          <t>FI-SE3</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>80</v>
+        <v>1200</v>
       </c>
       <c r="C52" t="n">
-        <v>80</v>
+        <v>1200</v>
       </c>
       <c r="D52" t="n">
-        <v>80</v>
+        <v>1200</v>
       </c>
       <c r="E52" t="n">
-        <v>80</v>
+        <v>1200</v>
       </c>
       <c r="F52" t="n">
-        <v>80</v>
+        <v>1200</v>
       </c>
       <c r="G52" t="n">
-        <v>80</v>
+        <v>1200</v>
       </c>
       <c r="H52" t="n">
-        <v>80</v>
+        <v>1200</v>
       </c>
       <c r="I52" t="n">
-        <v>80</v>
+        <v>1200</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FI-SE1</t>
+          <t>FR-IE</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="C53" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="D53" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="E53" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="F53" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="G53" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="H53" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="I53" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -3246,93 +3246,93 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FI-SE3</t>
+          <t>FR-ITn</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1200</v>
+        <v>4485</v>
       </c>
       <c r="C54" t="n">
-        <v>1200</v>
+        <v>1995</v>
       </c>
       <c r="D54" t="n">
-        <v>1200</v>
+        <v>4338</v>
       </c>
       <c r="E54" t="n">
-        <v>1200</v>
+        <v>2160</v>
       </c>
       <c r="F54" t="n">
-        <v>1200</v>
+        <v>4044</v>
       </c>
       <c r="G54" t="n">
-        <v>1200</v>
+        <v>1870</v>
       </c>
       <c r="H54" t="n">
-        <v>1200</v>
+        <v>3817</v>
       </c>
       <c r="I54" t="n">
-        <v>1200</v>
+        <v>2055</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FR-IE</t>
+          <t>FR-UKgb</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="C55" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="D55" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="E55" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="F55" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="G55" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="H55" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="I55" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="L55" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="M55" t="n">
         <v>2</v>
@@ -3350,99 +3350,99 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FR-ITn</t>
+          <t>GR-ITs</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4485</v>
+        <v>500</v>
       </c>
       <c r="C56" t="n">
-        <v>1995</v>
+        <v>500</v>
       </c>
       <c r="D56" t="n">
-        <v>4338</v>
+        <v>500</v>
       </c>
       <c r="E56" t="n">
-        <v>2160</v>
+        <v>500</v>
       </c>
       <c r="F56" t="n">
-        <v>4044</v>
+        <v>500</v>
       </c>
       <c r="G56" t="n">
-        <v>1870</v>
+        <v>500</v>
       </c>
       <c r="H56" t="n">
-        <v>3817</v>
+        <v>500</v>
       </c>
       <c r="I56" t="n">
-        <v>2055</v>
+        <v>500</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FR-UKgb</t>
+          <t>GR-MK</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="C57" t="n">
-        <v>4000</v>
+        <v>850</v>
       </c>
       <c r="D57" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="E57" t="n">
-        <v>4000</v>
+        <v>850</v>
       </c>
       <c r="F57" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="G57" t="n">
-        <v>4000</v>
+        <v>850</v>
       </c>
       <c r="H57" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="I57" t="n">
-        <v>4000</v>
+        <v>850</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -3454,84 +3454,84 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GR-ITs</t>
+          <t>HR-HU</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="C58" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D58" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E58" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F58" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G58" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H58" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="I58" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GR-MK</t>
+          <t>HR-RS</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1100</v>
+        <v>150</v>
       </c>
       <c r="C59" t="n">
-        <v>850</v>
+        <v>150</v>
       </c>
       <c r="D59" t="n">
-        <v>1100</v>
+        <v>150</v>
       </c>
       <c r="E59" t="n">
-        <v>850</v>
+        <v>150</v>
       </c>
       <c r="F59" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="G59" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="H59" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="I59" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
@@ -3558,32 +3558,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HR-HU</t>
+          <t>HR-SI</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="C60" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="D60" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="E60" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F60" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="G60" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="H60" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="I60" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -3610,32 +3610,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HR-RS</t>
+          <t>HU-RO</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>150</v>
+        <v>1617</v>
       </c>
       <c r="C61" t="n">
-        <v>150</v>
+        <v>1335</v>
       </c>
       <c r="D61" t="n">
-        <v>150</v>
+        <v>1617</v>
       </c>
       <c r="E61" t="n">
-        <v>150</v>
+        <v>1335</v>
       </c>
       <c r="F61" t="n">
-        <v>300</v>
+        <v>1617</v>
       </c>
       <c r="G61" t="n">
-        <v>300</v>
+        <v>1335</v>
       </c>
       <c r="H61" t="n">
-        <v>300</v>
+        <v>1617</v>
       </c>
       <c r="I61" t="n">
-        <v>300</v>
+        <v>1335</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -3662,32 +3662,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HR-SI</t>
+          <t>HU-RS</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1500</v>
+        <v>873</v>
       </c>
       <c r="C62" t="n">
-        <v>1500</v>
+        <v>1337</v>
       </c>
       <c r="D62" t="n">
-        <v>1500</v>
+        <v>873</v>
       </c>
       <c r="E62" t="n">
-        <v>1500</v>
+        <v>1337</v>
       </c>
       <c r="F62" t="n">
-        <v>1500</v>
+        <v>863</v>
       </c>
       <c r="G62" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="H62" t="n">
-        <v>1500</v>
+        <v>863</v>
       </c>
       <c r="I62" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -3714,32 +3714,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HU-RO</t>
+          <t>HU-SI</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1617</v>
+        <v>1200</v>
       </c>
       <c r="C63" t="n">
-        <v>1335</v>
+        <v>1200</v>
       </c>
       <c r="D63" t="n">
-        <v>1617</v>
+        <v>1200</v>
       </c>
       <c r="E63" t="n">
-        <v>1335</v>
+        <v>1200</v>
       </c>
       <c r="F63" t="n">
-        <v>1617</v>
+        <v>1200</v>
       </c>
       <c r="G63" t="n">
-        <v>1335</v>
+        <v>1200</v>
       </c>
       <c r="H63" t="n">
-        <v>1617</v>
+        <v>1200</v>
       </c>
       <c r="I63" t="n">
-        <v>1335</v>
+        <v>1200</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -3766,32 +3766,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HU-RS</t>
+          <t>HU-SK</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>873</v>
+        <v>1900</v>
       </c>
       <c r="C64" t="n">
-        <v>1337</v>
+        <v>3273</v>
       </c>
       <c r="D64" t="n">
-        <v>873</v>
+        <v>1900</v>
       </c>
       <c r="E64" t="n">
-        <v>1337</v>
+        <v>3273</v>
       </c>
       <c r="F64" t="n">
-        <v>863</v>
+        <v>1900</v>
       </c>
       <c r="G64" t="n">
-        <v>1440</v>
+        <v>3273</v>
       </c>
       <c r="H64" t="n">
-        <v>863</v>
+        <v>1900</v>
       </c>
       <c r="I64" t="n">
-        <v>1440</v>
+        <v>3273</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -3818,84 +3818,84 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HU-SI</t>
+          <t>IE-UKgb</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="C65" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="D65" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E65" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="F65" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="G65" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H65" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="I65" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HU-SK</t>
+          <t>IE-UKni</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1900</v>
+        <v>300</v>
       </c>
       <c r="C66" t="n">
-        <v>3273</v>
+        <v>300</v>
       </c>
       <c r="D66" t="n">
-        <v>1900</v>
+        <v>300</v>
       </c>
       <c r="E66" t="n">
-        <v>3273</v>
+        <v>300</v>
       </c>
       <c r="F66" t="n">
-        <v>1900</v>
+        <v>300</v>
       </c>
       <c r="G66" t="n">
-        <v>3273</v>
+        <v>300</v>
       </c>
       <c r="H66" t="n">
-        <v>1900</v>
+        <v>300</v>
       </c>
       <c r="I66" t="n">
-        <v>3273</v>
+        <v>300</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -3922,84 +3922,84 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IE-UKgb</t>
+          <t>ITca-ITs</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1000</v>
+        <v>2650</v>
       </c>
       <c r="C67" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="D67" t="n">
-        <v>1000</v>
+        <v>2650</v>
       </c>
       <c r="E67" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="F67" t="n">
-        <v>1000</v>
+        <v>2650</v>
       </c>
       <c r="G67" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="H67" t="n">
-        <v>1000</v>
+        <v>2650</v>
       </c>
       <c r="I67" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IE-UKni</t>
+          <t>ITca-ITsic</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="C68" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="D68" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="E68" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="F68" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="G68" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="H68" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="I68" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -4026,84 +4026,84 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ITca-ITs</t>
+          <t>ITcn-ITcs</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2650</v>
+        <v>3500</v>
       </c>
       <c r="C69" t="n">
-        <v>1400</v>
+        <v>4500</v>
       </c>
       <c r="D69" t="n">
-        <v>2650</v>
+        <v>4600</v>
       </c>
       <c r="E69" t="n">
-        <v>1400</v>
+        <v>4500</v>
       </c>
       <c r="F69" t="n">
-        <v>2650</v>
+        <v>3500</v>
       </c>
       <c r="G69" t="n">
-        <v>1400</v>
+        <v>4500</v>
       </c>
       <c r="H69" t="n">
-        <v>2650</v>
+        <v>4600</v>
       </c>
       <c r="I69" t="n">
-        <v>1400</v>
+        <v>4500</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ITca-ITsic</t>
+          <t>ITcn-ITn</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2000</v>
+        <v>3400</v>
       </c>
       <c r="C70" t="n">
-        <v>2000</v>
+        <v>5400</v>
       </c>
       <c r="D70" t="n">
-        <v>2000</v>
+        <v>4600</v>
       </c>
       <c r="E70" t="n">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="F70" t="n">
-        <v>2000</v>
+        <v>3400</v>
       </c>
       <c r="G70" t="n">
-        <v>2000</v>
+        <v>5400</v>
       </c>
       <c r="H70" t="n">
-        <v>2000</v>
+        <v>4600</v>
       </c>
       <c r="I70" t="n">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -4130,292 +4130,292 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ITcn-ITcs</t>
+          <t>ITcs-ITs</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="C71" t="n">
-        <v>4500</v>
+        <v>5700</v>
       </c>
       <c r="D71" t="n">
-        <v>4600</v>
+        <v>2900</v>
       </c>
       <c r="E71" t="n">
-        <v>4500</v>
+        <v>5700</v>
       </c>
       <c r="F71" t="n">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="G71" t="n">
-        <v>4500</v>
+        <v>5700</v>
       </c>
       <c r="H71" t="n">
-        <v>4600</v>
+        <v>2900</v>
       </c>
       <c r="I71" t="n">
-        <v>4500</v>
+        <v>5700</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ITcn-ITn</t>
+          <t>ITcs-ITsar</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3400</v>
+        <v>720</v>
       </c>
       <c r="C72" t="n">
-        <v>5400</v>
+        <v>900</v>
       </c>
       <c r="D72" t="n">
-        <v>4600</v>
+        <v>720</v>
       </c>
       <c r="E72" t="n">
-        <v>4500</v>
+        <v>870</v>
       </c>
       <c r="F72" t="n">
-        <v>3400</v>
+        <v>720</v>
       </c>
       <c r="G72" t="n">
-        <v>5400</v>
+        <v>900</v>
       </c>
       <c r="H72" t="n">
-        <v>4600</v>
+        <v>720</v>
       </c>
       <c r="I72" t="n">
-        <v>4500</v>
+        <v>870</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ITcs-ITs</t>
+          <t>ITcs-ME</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2900</v>
+        <v>1200</v>
       </c>
       <c r="C73" t="n">
-        <v>5700</v>
+        <v>1200</v>
       </c>
       <c r="D73" t="n">
-        <v>2900</v>
+        <v>1200</v>
       </c>
       <c r="E73" t="n">
-        <v>5700</v>
+        <v>1200</v>
       </c>
       <c r="F73" t="n">
-        <v>2900</v>
+        <v>1200</v>
       </c>
       <c r="G73" t="n">
-        <v>5700</v>
+        <v>1200</v>
       </c>
       <c r="H73" t="n">
-        <v>2900</v>
+        <v>1200</v>
       </c>
       <c r="I73" t="n">
-        <v>5700</v>
+        <v>1200</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ITcs-ITsar</t>
+          <t>ITn-SI</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>720</v>
+        <v>1260</v>
       </c>
       <c r="C74" t="n">
-        <v>900</v>
+        <v>1353</v>
       </c>
       <c r="D74" t="n">
-        <v>720</v>
+        <v>1280</v>
       </c>
       <c r="E74" t="n">
-        <v>870</v>
+        <v>1241</v>
       </c>
       <c r="F74" t="n">
-        <v>720</v>
+        <v>1220</v>
       </c>
       <c r="G74" t="n">
-        <v>900</v>
+        <v>1134</v>
       </c>
       <c r="H74" t="n">
-        <v>720</v>
+        <v>1245</v>
       </c>
       <c r="I74" t="n">
-        <v>870</v>
+        <v>1094</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ITcs-ME</t>
+          <t>ITsic-MT</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="C75" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="D75" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="E75" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="F75" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="G75" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="H75" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="I75" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ITn-SI</t>
+          <t>LT-LV</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1260</v>
+        <v>1134</v>
       </c>
       <c r="C76" t="n">
-        <v>1353</v>
+        <v>750</v>
       </c>
       <c r="D76" t="n">
-        <v>1280</v>
+        <v>1134</v>
       </c>
       <c r="E76" t="n">
-        <v>1241</v>
+        <v>750</v>
       </c>
       <c r="F76" t="n">
-        <v>1220</v>
+        <v>1134</v>
       </c>
       <c r="G76" t="n">
+        <v>750</v>
+      </c>
+      <c r="H76" t="n">
         <v>1134</v>
       </c>
-      <c r="H76" t="n">
-        <v>1245</v>
-      </c>
       <c r="I76" t="n">
-        <v>1094</v>
+        <v>750</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
@@ -4442,32 +4442,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ITsic-MT</t>
+          <t>LT-PL</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="C77" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="D77" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="E77" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="F77" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="G77" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="H77" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="I77" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
@@ -4494,84 +4494,84 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LT-LV</t>
+          <t>LT-SE4</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1134</v>
+        <v>700</v>
       </c>
       <c r="C78" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="D78" t="n">
-        <v>1134</v>
+        <v>700</v>
       </c>
       <c r="E78" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="F78" t="n">
-        <v>1134</v>
+        <v>700</v>
       </c>
       <c r="G78" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="H78" t="n">
-        <v>1134</v>
+        <v>700</v>
       </c>
       <c r="I78" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LT-PL</t>
+          <t>ME-RS</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>700</v>
+        <v>440</v>
       </c>
       <c r="C79" t="n">
-        <v>700</v>
+        <v>1140</v>
       </c>
       <c r="D79" t="n">
-        <v>700</v>
+        <v>440</v>
       </c>
       <c r="E79" t="n">
-        <v>700</v>
+        <v>1140</v>
       </c>
       <c r="F79" t="n">
-        <v>700</v>
+        <v>440</v>
       </c>
       <c r="G79" t="n">
-        <v>700</v>
+        <v>1140</v>
       </c>
       <c r="H79" t="n">
-        <v>700</v>
+        <v>440</v>
       </c>
       <c r="I79" t="n">
-        <v>700</v>
+        <v>1140</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
@@ -4598,197 +4598,197 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LT-SE4</t>
+          <t>MK-RS</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="C80" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="D80" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E80" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F80" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G80" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H80" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I80" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ME-RS</t>
+          <t>NL-NLll</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>440</v>
+        <v>1800</v>
       </c>
       <c r="C81" t="n">
-        <v>1140</v>
+        <v>2000</v>
       </c>
       <c r="D81" t="n">
-        <v>440</v>
+        <v>1800</v>
       </c>
       <c r="E81" t="n">
-        <v>1140</v>
+        <v>2000</v>
       </c>
       <c r="F81" t="n">
-        <v>440</v>
+        <v>1800</v>
       </c>
       <c r="G81" t="n">
-        <v>1140</v>
+        <v>2000</v>
       </c>
       <c r="H81" t="n">
-        <v>440</v>
+        <v>1800</v>
       </c>
       <c r="I81" t="n">
-        <v>1140</v>
+        <v>2000</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MK-RS</t>
+          <t>NL-NOs</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="C82" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D82" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E82" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F82" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G82" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="H82" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="I82" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NL-NOs</t>
+          <t>NL-UKgb</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="C83" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="D83" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E83" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="F83" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="G83" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="H83" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="I83" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="J83" t="b">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="L83" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="M83" t="n">
         <v>2</v>
@@ -4797,93 +4797,93 @@
         <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>0.06</v>
+        <v>0.012</v>
       </c>
       <c r="P83" t="n">
-        <v>0.06</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NL-UKgb</t>
+          <t>NOm-NOn</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="C84" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="D84" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="E84" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="F84" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="G84" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H84" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="I84" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="J84" t="b">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NOm-NOn</t>
+          <t>NOm-NOs</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="C85" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="D85" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="E85" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="F85" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="G85" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H85" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="I85" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="J85" t="b">
         <v>0</v>
@@ -4910,29 +4910,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NOm-NOs</t>
+          <t>NOm-SE2</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="C86" t="n">
         <v>1000</v>
       </c>
       <c r="D86" t="n">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="E86" t="n">
         <v>1000</v>
       </c>
       <c r="F86" t="n">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="G86" t="n">
         <v>1000</v>
       </c>
       <c r="H86" t="n">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="I86" t="n">
         <v>1000</v>
@@ -4962,32 +4962,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NOm-SE2</t>
+          <t>NOn-SE1</t>
         </is>
       </c>
       <c r="B87" t="n">
+        <v>700</v>
+      </c>
+      <c r="C87" t="n">
         <v>600</v>
       </c>
-      <c r="C87" t="n">
-        <v>1000</v>
-      </c>
       <c r="D87" t="n">
+        <v>700</v>
+      </c>
+      <c r="E87" t="n">
         <v>600</v>
       </c>
-      <c r="E87" t="n">
-        <v>1000</v>
-      </c>
       <c r="F87" t="n">
+        <v>700</v>
+      </c>
+      <c r="G87" t="n">
         <v>600</v>
       </c>
-      <c r="G87" t="n">
-        <v>1000</v>
-      </c>
       <c r="H87" t="n">
+        <v>700</v>
+      </c>
+      <c r="I87" t="n">
         <v>600</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1000</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
@@ -5014,32 +5014,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NOn-SE1</t>
+          <t>NOn-SE2</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="C88" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="D88" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="E88" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="F88" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="G88" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H88" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="I88" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="J88" t="b">
         <v>0</v>
@@ -5066,32 +5066,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NOn-SE2</t>
+          <t>NOs-SE3</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>250</v>
+        <v>2145</v>
       </c>
       <c r="C89" t="n">
-        <v>300</v>
+        <v>2095</v>
       </c>
       <c r="D89" t="n">
-        <v>250</v>
+        <v>2145</v>
       </c>
       <c r="E89" t="n">
-        <v>300</v>
+        <v>2095</v>
       </c>
       <c r="F89" t="n">
-        <v>250</v>
+        <v>2145</v>
       </c>
       <c r="G89" t="n">
-        <v>300</v>
+        <v>2095</v>
       </c>
       <c r="H89" t="n">
-        <v>250</v>
+        <v>2145</v>
       </c>
       <c r="I89" t="n">
-        <v>300</v>
+        <v>2095</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
@@ -5118,99 +5118,99 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NOs-SE3</t>
+          <t>NOs-UKgb</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2145</v>
+        <v>1444</v>
       </c>
       <c r="C90" t="n">
-        <v>2095</v>
+        <v>1444</v>
       </c>
       <c r="D90" t="n">
-        <v>2145</v>
+        <v>1444</v>
       </c>
       <c r="E90" t="n">
-        <v>2095</v>
+        <v>1444</v>
       </c>
       <c r="F90" t="n">
-        <v>2145</v>
+        <v>1444</v>
       </c>
       <c r="G90" t="n">
-        <v>2095</v>
+        <v>1444</v>
       </c>
       <c r="H90" t="n">
-        <v>2145</v>
+        <v>1444</v>
       </c>
       <c r="I90" t="n">
-        <v>2095</v>
+        <v>1444</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1444</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1444</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NOs-UKgb</t>
+          <t>PL-SE4</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1444</v>
+        <v>600</v>
       </c>
       <c r="C91" t="n">
-        <v>1444</v>
+        <v>600</v>
       </c>
       <c r="D91" t="n">
-        <v>1444</v>
+        <v>600</v>
       </c>
       <c r="E91" t="n">
-        <v>1444</v>
+        <v>600</v>
       </c>
       <c r="F91" t="n">
-        <v>1444</v>
+        <v>600</v>
       </c>
       <c r="G91" t="n">
-        <v>1444</v>
+        <v>600</v>
       </c>
       <c r="H91" t="n">
-        <v>1444</v>
+        <v>600</v>
       </c>
       <c r="I91" t="n">
-        <v>1444</v>
+        <v>600</v>
       </c>
       <c r="J91" t="b">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>1444</v>
+        <v>600</v>
       </c>
       <c r="L91" t="n">
-        <v>1444</v>
+        <v>600</v>
       </c>
       <c r="M91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O91" t="n">
         <v>0.06</v>
@@ -5222,84 +5222,84 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PL-SE4</t>
+          <t>RO-RS</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>600</v>
+        <v>2024</v>
       </c>
       <c r="C92" t="n">
-        <v>600</v>
+        <v>1843</v>
       </c>
       <c r="D92" t="n">
-        <v>600</v>
+        <v>2024</v>
       </c>
       <c r="E92" t="n">
-        <v>600</v>
+        <v>1843</v>
       </c>
       <c r="F92" t="n">
-        <v>600</v>
+        <v>2013</v>
       </c>
       <c r="G92" t="n">
-        <v>600</v>
+        <v>1826</v>
       </c>
       <c r="H92" t="n">
-        <v>600</v>
+        <v>2013</v>
       </c>
       <c r="I92" t="n">
-        <v>600</v>
+        <v>1826</v>
       </c>
       <c r="J92" t="b">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PL-SK</t>
+          <t>SE1-SE2</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>894</v>
+        <v>3300</v>
       </c>
       <c r="C93" t="n">
-        <v>880</v>
+        <v>3300</v>
       </c>
       <c r="D93" t="n">
-        <v>894</v>
+        <v>3300</v>
       </c>
       <c r="E93" t="n">
-        <v>880</v>
+        <v>3300</v>
       </c>
       <c r="F93" t="n">
-        <v>894</v>
+        <v>3300</v>
       </c>
       <c r="G93" t="n">
-        <v>880</v>
+        <v>3300</v>
       </c>
       <c r="H93" t="n">
-        <v>894</v>
+        <v>3300</v>
       </c>
       <c r="I93" t="n">
-        <v>880</v>
+        <v>3300</v>
       </c>
       <c r="J93" t="b">
         <v>0</v>
@@ -5326,32 +5326,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>RO-RS</t>
+          <t>SE2-SE3</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2024</v>
+        <v>8100</v>
       </c>
       <c r="C94" t="n">
-        <v>1843</v>
+        <v>8100</v>
       </c>
       <c r="D94" t="n">
-        <v>2024</v>
+        <v>8100</v>
       </c>
       <c r="E94" t="n">
-        <v>1843</v>
+        <v>8100</v>
       </c>
       <c r="F94" t="n">
-        <v>2013</v>
+        <v>8100</v>
       </c>
       <c r="G94" t="n">
-        <v>1826</v>
+        <v>8100</v>
       </c>
       <c r="H94" t="n">
-        <v>2013</v>
+        <v>8100</v>
       </c>
       <c r="I94" t="n">
-        <v>1826</v>
+        <v>8100</v>
       </c>
       <c r="J94" t="b">
         <v>0</v>
@@ -5378,208 +5378,104 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SE1-SE2</t>
+          <t>SE3-SE4</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3300</v>
+        <v>6200</v>
       </c>
       <c r="C95" t="n">
-        <v>3300</v>
+        <v>2800</v>
       </c>
       <c r="D95" t="n">
-        <v>3300</v>
+        <v>6200</v>
       </c>
       <c r="E95" t="n">
-        <v>3300</v>
+        <v>2800</v>
       </c>
       <c r="F95" t="n">
-        <v>3300</v>
+        <v>6200</v>
       </c>
       <c r="G95" t="n">
-        <v>3300</v>
+        <v>2800</v>
       </c>
       <c r="H95" t="n">
-        <v>3300</v>
+        <v>6200</v>
       </c>
       <c r="I95" t="n">
-        <v>3300</v>
+        <v>2800</v>
       </c>
       <c r="J95" t="b">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SE2-SE3</t>
+          <t>UKgb-UKni</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>8100</v>
+        <v>500</v>
       </c>
       <c r="C96" t="n">
-        <v>8100</v>
+        <v>500</v>
       </c>
       <c r="D96" t="n">
-        <v>8100</v>
+        <v>500</v>
       </c>
       <c r="E96" t="n">
-        <v>8100</v>
+        <v>500</v>
       </c>
       <c r="F96" t="n">
-        <v>8100</v>
+        <v>500</v>
       </c>
       <c r="G96" t="n">
-        <v>8100</v>
+        <v>500</v>
       </c>
       <c r="H96" t="n">
-        <v>8100</v>
+        <v>500</v>
       </c>
       <c r="I96" t="n">
-        <v>8100</v>
+        <v>500</v>
       </c>
       <c r="J96" t="b">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>SE3-SE4</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>6200</v>
-      </c>
-      <c r="C97" t="n">
-        <v>2800</v>
-      </c>
-      <c r="D97" t="n">
-        <v>6200</v>
-      </c>
-      <c r="E97" t="n">
-        <v>2800</v>
-      </c>
-      <c r="F97" t="n">
-        <v>6200</v>
-      </c>
-      <c r="G97" t="n">
-        <v>2800</v>
-      </c>
-      <c r="H97" t="n">
-        <v>6200</v>
-      </c>
-      <c r="I97" t="n">
-        <v>2800</v>
-      </c>
-      <c r="J97" t="b">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>800</v>
-      </c>
-      <c r="L97" t="n">
-        <v>800</v>
-      </c>
-      <c r="M97" t="n">
-        <v>2</v>
-      </c>
-      <c r="N97" t="n">
-        <v>2</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>UKgb-UKni</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>500</v>
-      </c>
-      <c r="C98" t="n">
-        <v>500</v>
-      </c>
-      <c r="D98" t="n">
-        <v>500</v>
-      </c>
-      <c r="E98" t="n">
-        <v>500</v>
-      </c>
-      <c r="F98" t="n">
-        <v>500</v>
-      </c>
-      <c r="G98" t="n">
-        <v>500</v>
-      </c>
-      <c r="H98" t="n">
-        <v>500</v>
-      </c>
-      <c r="I98" t="n">
-        <v>500</v>
-      </c>
-      <c r="J98" t="b">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>500</v>
-      </c>
-      <c r="L98" t="n">
-        <v>500</v>
-      </c>
-      <c r="M98" t="n">
-        <v>2</v>
-      </c>
-      <c r="N98" t="n">
-        <v>2</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="P98" t="n">
         <v>0.08400000000000001</v>
       </c>
     </row>
@@ -5594,7 +5490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7138,32 +7034,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CZ-PL</t>
+          <t>CZ-SK</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1050</v>
+        <v>1900</v>
       </c>
       <c r="C30" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="D30" t="n">
-        <v>1050</v>
+        <v>1900</v>
       </c>
       <c r="E30" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="F30" t="n">
-        <v>1050</v>
+        <v>1900</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="H30" t="n">
-        <v>1050</v>
+        <v>1900</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -7190,32 +7086,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CZ-SK</t>
+          <t>DE-DEkf</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1900</v>
+        <v>400</v>
       </c>
       <c r="C31" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="D31" t="n">
-        <v>1900</v>
+        <v>400</v>
       </c>
       <c r="E31" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="F31" t="n">
-        <v>1900</v>
+        <v>400</v>
       </c>
       <c r="G31" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="H31" t="n">
-        <v>1900</v>
+        <v>400</v>
       </c>
       <c r="I31" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -7242,99 +7138,99 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DE-DEkf</t>
+          <t>DE-DKbh</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="C32" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="D32" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="E32" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="F32" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="G32" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="H32" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="I32" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>0.0888888888888888</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>0.0888888888888888</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DE-DKbh</t>
+          <t>DE-DKe</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2000</v>
+        <v>585</v>
       </c>
       <c r="C33" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="D33" t="n">
-        <v>2000</v>
+        <v>585</v>
       </c>
       <c r="E33" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="F33" t="n">
-        <v>2000</v>
+        <v>585</v>
       </c>
       <c r="G33" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="H33" t="n">
-        <v>2000</v>
+        <v>585</v>
       </c>
       <c r="I33" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2000</v>
+        <v>585</v>
       </c>
       <c r="L33" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>0.0888888888888888</v>
@@ -7346,84 +7242,84 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DE-DKe</t>
+          <t>DE-DKw</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>585</v>
+        <v>3500</v>
       </c>
       <c r="C34" t="n">
-        <v>600</v>
+        <v>3500</v>
       </c>
       <c r="D34" t="n">
-        <v>585</v>
+        <v>3500</v>
       </c>
       <c r="E34" t="n">
-        <v>600</v>
+        <v>3500</v>
       </c>
       <c r="F34" t="n">
-        <v>585</v>
+        <v>3500</v>
       </c>
       <c r="G34" t="n">
-        <v>600</v>
+        <v>3500</v>
       </c>
       <c r="H34" t="n">
-        <v>585</v>
+        <v>3500</v>
       </c>
       <c r="I34" t="n">
-        <v>600</v>
+        <v>3500</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>585</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0888888888888888</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0888888888888888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DE-DKw</t>
+          <t>DE-FR</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="C35" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="D35" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="E35" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="F35" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="G35" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="H35" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="I35" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -7450,32 +7346,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DE-FR</t>
+          <t>DE-LU</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="C36" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="D36" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="E36" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="F36" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="G36" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="H36" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="I36" t="n">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -7502,32 +7398,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DE-LU</t>
+          <t>DE-NL</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="C37" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="D37" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="E37" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="F37" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="G37" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="H37" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="I37" t="n">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -7554,99 +7450,99 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DE-NL</t>
+          <t>DE-NOs</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="C38" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="D38" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="E38" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="F38" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="G38" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="H38" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="I38" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DE-NOs</t>
+          <t>DE-SE4</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="C39" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="D39" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="E39" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="F39" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="G39" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="H39" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="I39" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="L39" t="n">
-        <v>1400</v>
+        <v>615</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
         <v>0.02</v>
@@ -7658,203 +7554,203 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DE-PL</t>
+          <t>DE-UKgb</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="C40" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="D40" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="E40" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="F40" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="G40" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="H40" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="I40" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DE-SE4</t>
+          <t>DEkf-DKkf</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="C41" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="D41" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="E41" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="F41" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="G41" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="H41" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="I41" t="n">
-        <v>615</v>
+        <v>400</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DE-UKgb</t>
+          <t>DKbh-DKe</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="C42" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="D42" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="E42" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="F42" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="G42" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="H42" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="I42" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="L42" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>0.02</v>
+        <v>0.0888888888888888</v>
       </c>
       <c r="P42" t="n">
-        <v>0.02</v>
+        <v>0.0888888888888888</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DEkf-DKkf</t>
+          <t>DKe-DKkf</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="D43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="H43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I43" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -7866,47 +7762,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DKbh-DKe</t>
+          <t>DKe-DKw</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="C44" t="n">
-        <v>1200</v>
+        <v>590</v>
       </c>
       <c r="D44" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="E44" t="n">
-        <v>1200</v>
+        <v>590</v>
       </c>
       <c r="F44" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="G44" t="n">
-        <v>1200</v>
+        <v>590</v>
       </c>
       <c r="H44" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="I44" t="n">
-        <v>1200</v>
+        <v>590</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="L44" t="n">
-        <v>1200</v>
+        <v>590</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
         <v>0.0888888888888888</v>
@@ -7918,47 +7814,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DKe-DKkf</t>
+          <t>DKe-SE4</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>600</v>
+        <v>1700</v>
       </c>
       <c r="C45" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="D45" t="n">
-        <v>600</v>
+        <v>1700</v>
       </c>
       <c r="E45" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="F45" t="n">
-        <v>600</v>
+        <v>1267</v>
       </c>
       <c r="G45" t="n">
-        <v>600</v>
+        <v>867</v>
       </c>
       <c r="H45" t="n">
-        <v>600</v>
+        <v>1267</v>
       </c>
       <c r="I45" t="n">
-        <v>600</v>
+        <v>867</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -7970,41 +7866,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DKe-DKw</t>
+          <t>DKw-NL</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="C46" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="D46" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E46" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="F46" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G46" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="H46" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I46" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L46" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
@@ -8022,99 +7918,99 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DKe-SE4</t>
+          <t>DKw-NOs</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1700</v>
+        <v>1632</v>
       </c>
       <c r="C47" t="n">
-        <v>1300</v>
+        <v>1632</v>
       </c>
       <c r="D47" t="n">
-        <v>1700</v>
+        <v>1632</v>
       </c>
       <c r="E47" t="n">
-        <v>1300</v>
+        <v>1632</v>
       </c>
       <c r="F47" t="n">
-        <v>1267</v>
+        <v>1632</v>
       </c>
       <c r="G47" t="n">
-        <v>867</v>
+        <v>1632</v>
       </c>
       <c r="H47" t="n">
-        <v>1267</v>
+        <v>1632</v>
       </c>
       <c r="I47" t="n">
-        <v>867</v>
+        <v>1632</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1632</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1632</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>0.0888888888888888</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>0.0888888888888888</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DKw-NL</t>
+          <t>DKw-SE3</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="C48" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="D48" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="E48" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="F48" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="G48" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="H48" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="I48" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="L48" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
         <v>0.0888888888888888</v>
@@ -8126,47 +8022,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DKw-NOs</t>
+          <t>DKw-UKgb</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="C49" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="D49" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="E49" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="F49" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="G49" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="H49" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="I49" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="L49" t="n">
-        <v>1632</v>
+        <v>1400</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O49" t="n">
         <v>0.0888888888888888</v>
@@ -8178,188 +8074,188 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DKw-SE3</t>
+          <t>EE-FI</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>715</v>
+        <v>1716</v>
       </c>
       <c r="C50" t="n">
-        <v>715</v>
+        <v>1716</v>
       </c>
       <c r="D50" t="n">
-        <v>715</v>
+        <v>1716</v>
       </c>
       <c r="E50" t="n">
-        <v>715</v>
+        <v>1716</v>
       </c>
       <c r="F50" t="n">
-        <v>715</v>
+        <v>1716</v>
       </c>
       <c r="G50" t="n">
-        <v>715</v>
+        <v>1716</v>
       </c>
       <c r="H50" t="n">
-        <v>715</v>
+        <v>1716</v>
       </c>
       <c r="I50" t="n">
-        <v>715</v>
+        <v>1716</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>715</v>
+        <v>1716</v>
       </c>
       <c r="L50" t="n">
-        <v>715</v>
+        <v>1716</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.11</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DKw-UKgb</t>
+          <t>EE-LV</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1400</v>
+        <v>1550</v>
       </c>
       <c r="C51" t="n">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="D51" t="n">
-        <v>1400</v>
+        <v>1550</v>
       </c>
       <c r="E51" t="n">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="F51" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="G51" t="n">
-        <v>1400</v>
+        <v>1130</v>
       </c>
       <c r="H51" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="I51" t="n">
-        <v>1400</v>
+        <v>1130</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0.0888888888888888</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0888888888888888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EE-FI</t>
+          <t>ES-FR</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1716</v>
+        <v>5400</v>
       </c>
       <c r="C52" t="n">
-        <v>1716</v>
+        <v>5300</v>
       </c>
       <c r="D52" t="n">
-        <v>1716</v>
+        <v>5600</v>
       </c>
       <c r="E52" t="n">
-        <v>1716</v>
+        <v>5300</v>
       </c>
       <c r="F52" t="n">
-        <v>1716</v>
+        <v>3600</v>
       </c>
       <c r="G52" t="n">
-        <v>1716</v>
+        <v>5300</v>
       </c>
       <c r="H52" t="n">
-        <v>1716</v>
+        <v>5500</v>
       </c>
       <c r="I52" t="n">
-        <v>1716</v>
+        <v>5100</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>1716</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>1716</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EE-LV</t>
+          <t>ES-PT</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1550</v>
+        <v>4200</v>
       </c>
       <c r="C53" t="n">
-        <v>1700</v>
+        <v>3500</v>
       </c>
       <c r="D53" t="n">
-        <v>1550</v>
+        <v>4200</v>
       </c>
       <c r="E53" t="n">
-        <v>1700</v>
+        <v>3500</v>
       </c>
       <c r="F53" t="n">
-        <v>1350</v>
+        <v>4200</v>
       </c>
       <c r="G53" t="n">
-        <v>1130</v>
+        <v>3500</v>
       </c>
       <c r="H53" t="n">
-        <v>1350</v>
+        <v>4200</v>
       </c>
       <c r="I53" t="n">
-        <v>1130</v>
+        <v>3500</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
@@ -8386,84 +8282,84 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ES-FR</t>
+          <t>FI-NOn</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>5400</v>
+        <v>150</v>
       </c>
       <c r="C54" t="n">
-        <v>5300</v>
+        <v>150</v>
       </c>
       <c r="D54" t="n">
-        <v>5600</v>
+        <v>150</v>
       </c>
       <c r="E54" t="n">
-        <v>5300</v>
+        <v>150</v>
       </c>
       <c r="F54" t="n">
-        <v>3600</v>
+        <v>150</v>
       </c>
       <c r="G54" t="n">
-        <v>5300</v>
+        <v>150</v>
       </c>
       <c r="H54" t="n">
-        <v>5500</v>
+        <v>150</v>
       </c>
       <c r="I54" t="n">
-        <v>5100</v>
+        <v>150</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ES-PT</t>
+          <t>FI-SE1</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="C55" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="D55" t="n">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="E55" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="F55" t="n">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="G55" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="H55" t="n">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="I55" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
@@ -8490,47 +8386,47 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FI-NOn</t>
+          <t>FI-SE3</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="C56" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="D56" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E56" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="F56" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="G56" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="H56" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="I56" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="L56" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O56" t="n">
         <v>0.03</v>
@@ -8542,47 +8438,47 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FI-SE1</t>
+          <t>FR-IE</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="C57" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="D57" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="E57" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="F57" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="G57" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="H57" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="I57" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8594,93 +8490,93 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FI-SE3</t>
+          <t>FR-ITn</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1200</v>
+        <v>4485</v>
       </c>
       <c r="C58" t="n">
-        <v>1200</v>
+        <v>1995</v>
       </c>
       <c r="D58" t="n">
-        <v>1200</v>
+        <v>4338</v>
       </c>
       <c r="E58" t="n">
-        <v>1200</v>
+        <v>2160</v>
       </c>
       <c r="F58" t="n">
-        <v>1200</v>
+        <v>4044</v>
       </c>
       <c r="G58" t="n">
-        <v>1200</v>
+        <v>1870</v>
       </c>
       <c r="H58" t="n">
-        <v>1200</v>
+        <v>3817</v>
       </c>
       <c r="I58" t="n">
-        <v>1200</v>
+        <v>2055</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FR-IE</t>
+          <t>FR-UKgb</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="C59" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="D59" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="E59" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="F59" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="G59" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="H59" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="I59" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="L59" t="n">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="M59" t="n">
         <v>2</v>
@@ -8698,99 +8594,99 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FR-ITn</t>
+          <t>GR-ITs</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4485</v>
+        <v>1500</v>
       </c>
       <c r="C60" t="n">
-        <v>1995</v>
+        <v>1500</v>
       </c>
       <c r="D60" t="n">
-        <v>4338</v>
+        <v>1500</v>
       </c>
       <c r="E60" t="n">
-        <v>2160</v>
+        <v>1500</v>
       </c>
       <c r="F60" t="n">
-        <v>4044</v>
+        <v>1500</v>
       </c>
       <c r="G60" t="n">
-        <v>1870</v>
+        <v>1500</v>
       </c>
       <c r="H60" t="n">
-        <v>3817</v>
+        <v>1500</v>
       </c>
       <c r="I60" t="n">
-        <v>2055</v>
+        <v>1500</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>0.0436</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>0.0436</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FR-UKgb</t>
+          <t>GR-MK</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="C61" t="n">
-        <v>4000</v>
+        <v>850</v>
       </c>
       <c r="D61" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="E61" t="n">
-        <v>4000</v>
+        <v>850</v>
       </c>
       <c r="F61" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="G61" t="n">
-        <v>4000</v>
+        <v>850</v>
       </c>
       <c r="H61" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="I61" t="n">
-        <v>4000</v>
+        <v>850</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8802,84 +8698,84 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GR-ITs</t>
+          <t>HR-HU</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="C62" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D62" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="E62" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="F62" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="G62" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="H62" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="I62" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>0.0436</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.0436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GR-MK</t>
+          <t>HR-RS</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1100</v>
+        <v>150</v>
       </c>
       <c r="C63" t="n">
-        <v>850</v>
+        <v>150</v>
       </c>
       <c r="D63" t="n">
-        <v>1100</v>
+        <v>150</v>
       </c>
       <c r="E63" t="n">
-        <v>850</v>
+        <v>150</v>
       </c>
       <c r="F63" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="G63" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="H63" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="I63" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -8906,32 +8802,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HR-HU</t>
+          <t>HR-SI</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="C64" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="D64" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="E64" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F64" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="G64" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="H64" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="I64" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -8958,32 +8854,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HR-RS</t>
+          <t>HU-RO</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>150</v>
+        <v>3027</v>
       </c>
       <c r="C65" t="n">
-        <v>150</v>
+        <v>2075</v>
       </c>
       <c r="D65" t="n">
-        <v>150</v>
+        <v>3027</v>
       </c>
       <c r="E65" t="n">
-        <v>150</v>
+        <v>2075</v>
       </c>
       <c r="F65" t="n">
-        <v>300</v>
+        <v>3027</v>
       </c>
       <c r="G65" t="n">
-        <v>300</v>
+        <v>2075</v>
       </c>
       <c r="H65" t="n">
-        <v>300</v>
+        <v>3027</v>
       </c>
       <c r="I65" t="n">
-        <v>300</v>
+        <v>2075</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -9010,32 +8906,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HR-SI</t>
+          <t>HU-RS</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1500</v>
+        <v>873</v>
       </c>
       <c r="C66" t="n">
-        <v>1500</v>
+        <v>1337</v>
       </c>
       <c r="D66" t="n">
-        <v>1500</v>
+        <v>873</v>
       </c>
       <c r="E66" t="n">
-        <v>1500</v>
+        <v>1337</v>
       </c>
       <c r="F66" t="n">
-        <v>1500</v>
+        <v>863</v>
       </c>
       <c r="G66" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="H66" t="n">
-        <v>1500</v>
+        <v>863</v>
       </c>
       <c r="I66" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -9062,32 +8958,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HU-RO</t>
+          <t>HU-SI</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3027</v>
+        <v>1200</v>
       </c>
       <c r="C67" t="n">
-        <v>2075</v>
+        <v>1200</v>
       </c>
       <c r="D67" t="n">
-        <v>3027</v>
+        <v>1200</v>
       </c>
       <c r="E67" t="n">
-        <v>2075</v>
+        <v>1200</v>
       </c>
       <c r="F67" t="n">
-        <v>3027</v>
+        <v>1200</v>
       </c>
       <c r="G67" t="n">
-        <v>2075</v>
+        <v>1200</v>
       </c>
       <c r="H67" t="n">
-        <v>3027</v>
+        <v>1200</v>
       </c>
       <c r="I67" t="n">
-        <v>2075</v>
+        <v>1200</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -9114,32 +9010,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HU-RS</t>
+          <t>HU-SK</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>873</v>
+        <v>1900</v>
       </c>
       <c r="C68" t="n">
-        <v>1337</v>
+        <v>3273</v>
       </c>
       <c r="D68" t="n">
-        <v>873</v>
+        <v>1900</v>
       </c>
       <c r="E68" t="n">
-        <v>1337</v>
+        <v>3273</v>
       </c>
       <c r="F68" t="n">
-        <v>863</v>
+        <v>1900</v>
       </c>
       <c r="G68" t="n">
-        <v>1440</v>
+        <v>3273</v>
       </c>
       <c r="H68" t="n">
-        <v>863</v>
+        <v>1900</v>
       </c>
       <c r="I68" t="n">
-        <v>1440</v>
+        <v>3273</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -9166,84 +9062,84 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HU-SI</t>
+          <t>IE-UKgb</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="C69" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="D69" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E69" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="F69" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="G69" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H69" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="I69" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HU-SK</t>
+          <t>IE-UKni</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1900</v>
+        <v>1250</v>
       </c>
       <c r="C70" t="n">
-        <v>3273</v>
+        <v>1200</v>
       </c>
       <c r="D70" t="n">
-        <v>1900</v>
+        <v>1250</v>
       </c>
       <c r="E70" t="n">
-        <v>3273</v>
+        <v>1200</v>
       </c>
       <c r="F70" t="n">
-        <v>1900</v>
+        <v>1250</v>
       </c>
       <c r="G70" t="n">
-        <v>3273</v>
+        <v>1200</v>
       </c>
       <c r="H70" t="n">
-        <v>1900</v>
+        <v>1250</v>
       </c>
       <c r="I70" t="n">
-        <v>3273</v>
+        <v>1200</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -9270,84 +9166,84 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IE-UKgb</t>
+          <t>ITca-ITs</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1000</v>
+        <v>3250</v>
       </c>
       <c r="C71" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D71" t="n">
-        <v>1000</v>
+        <v>3250</v>
       </c>
       <c r="E71" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F71" t="n">
-        <v>1000</v>
+        <v>3250</v>
       </c>
       <c r="G71" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H71" t="n">
-        <v>1000</v>
+        <v>3250</v>
       </c>
       <c r="I71" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IE-UKni</t>
+          <t>ITca-ITsic</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1250</v>
+        <v>2000</v>
       </c>
       <c r="C72" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="D72" t="n">
-        <v>1250</v>
+        <v>2000</v>
       </c>
       <c r="E72" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="F72" t="n">
-        <v>1250</v>
+        <v>2000</v>
       </c>
       <c r="G72" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H72" t="n">
-        <v>1250</v>
+        <v>2000</v>
       </c>
       <c r="I72" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
@@ -9374,84 +9270,84 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ITca-ITs</t>
+          <t>ITcn-ITcs</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3250</v>
+        <v>4100</v>
       </c>
       <c r="C73" t="n">
-        <v>2000</v>
+        <v>5900</v>
       </c>
       <c r="D73" t="n">
-        <v>3250</v>
+        <v>5200</v>
       </c>
       <c r="E73" t="n">
-        <v>2000</v>
+        <v>5900</v>
       </c>
       <c r="F73" t="n">
-        <v>3250</v>
+        <v>4100</v>
       </c>
       <c r="G73" t="n">
-        <v>2000</v>
+        <v>5900</v>
       </c>
       <c r="H73" t="n">
-        <v>3250</v>
+        <v>5200</v>
       </c>
       <c r="I73" t="n">
-        <v>2000</v>
+        <v>5900</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ITca-ITsic</t>
+          <t>ITcn-ITn</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2000</v>
+        <v>4100</v>
       </c>
       <c r="C74" t="n">
-        <v>2000</v>
+        <v>6100</v>
       </c>
       <c r="D74" t="n">
-        <v>2000</v>
+        <v>5300</v>
       </c>
       <c r="E74" t="n">
-        <v>2000</v>
+        <v>5200</v>
       </c>
       <c r="F74" t="n">
-        <v>2000</v>
+        <v>4100</v>
       </c>
       <c r="G74" t="n">
-        <v>2000</v>
+        <v>6100</v>
       </c>
       <c r="H74" t="n">
-        <v>2000</v>
+        <v>5300</v>
       </c>
       <c r="I74" t="n">
-        <v>2000</v>
+        <v>5200</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
@@ -9478,41 +9374,41 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ITcn-ITcs</t>
+          <t>ITcs-ITn</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4100</v>
+        <v>2100</v>
       </c>
       <c r="C75" t="n">
-        <v>5900</v>
+        <v>2100</v>
       </c>
       <c r="D75" t="n">
-        <v>5200</v>
+        <v>2100</v>
       </c>
       <c r="E75" t="n">
-        <v>5900</v>
+        <v>2100</v>
       </c>
       <c r="F75" t="n">
-        <v>4100</v>
+        <v>2100</v>
       </c>
       <c r="G75" t="n">
-        <v>5900</v>
+        <v>2100</v>
       </c>
       <c r="H75" t="n">
-        <v>5200</v>
+        <v>2100</v>
       </c>
       <c r="I75" t="n">
-        <v>5900</v>
+        <v>2100</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="L75" t="n">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="M75" t="n">
         <v>2</v>
@@ -9521,41 +9417,41 @@
         <v>2</v>
       </c>
       <c r="O75" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="P75" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ITcn-ITn</t>
+          <t>ITcs-ITs</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4100</v>
+        <v>3900</v>
       </c>
       <c r="C76" t="n">
-        <v>6100</v>
+        <v>6700</v>
       </c>
       <c r="D76" t="n">
-        <v>5300</v>
+        <v>3900</v>
       </c>
       <c r="E76" t="n">
-        <v>5200</v>
+        <v>6700</v>
       </c>
       <c r="F76" t="n">
-        <v>4100</v>
+        <v>3900</v>
       </c>
       <c r="G76" t="n">
-        <v>6100</v>
+        <v>6700</v>
       </c>
       <c r="H76" t="n">
-        <v>5300</v>
+        <v>3900</v>
       </c>
       <c r="I76" t="n">
-        <v>5200</v>
+        <v>6700</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
@@ -9582,41 +9478,41 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ITcs-ITn</t>
+          <t>ITcs-ITsar</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2100</v>
+        <v>720</v>
       </c>
       <c r="C77" t="n">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="D77" t="n">
-        <v>2100</v>
+        <v>720</v>
       </c>
       <c r="E77" t="n">
-        <v>2100</v>
+        <v>870</v>
       </c>
       <c r="F77" t="n">
-        <v>2100</v>
+        <v>720</v>
       </c>
       <c r="G77" t="n">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="H77" t="n">
-        <v>2100</v>
+        <v>720</v>
       </c>
       <c r="I77" t="n">
-        <v>2100</v>
+        <v>870</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>2100</v>
+        <v>720</v>
       </c>
       <c r="L77" t="n">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="M77" t="n">
         <v>2</v>
@@ -9625,102 +9521,102 @@
         <v>2</v>
       </c>
       <c r="O77" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
       <c r="P77" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ITcs-ITs</t>
+          <t>ITcs-ME</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3900</v>
+        <v>1200</v>
       </c>
       <c r="C78" t="n">
-        <v>6700</v>
+        <v>1200</v>
       </c>
       <c r="D78" t="n">
-        <v>3900</v>
+        <v>1200</v>
       </c>
       <c r="E78" t="n">
-        <v>6700</v>
+        <v>1200</v>
       </c>
       <c r="F78" t="n">
-        <v>3900</v>
+        <v>1200</v>
       </c>
       <c r="G78" t="n">
-        <v>6700</v>
+        <v>1200</v>
       </c>
       <c r="H78" t="n">
-        <v>3900</v>
+        <v>1200</v>
       </c>
       <c r="I78" t="n">
-        <v>6700</v>
+        <v>1200</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ITcs-ITsar</t>
+          <t>ITn-ITs</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>720</v>
+        <v>2100</v>
       </c>
       <c r="C79" t="n">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="D79" t="n">
-        <v>720</v>
+        <v>2100</v>
       </c>
       <c r="E79" t="n">
-        <v>870</v>
+        <v>2100</v>
       </c>
       <c r="F79" t="n">
-        <v>720</v>
+        <v>2100</v>
       </c>
       <c r="G79" t="n">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="H79" t="n">
-        <v>720</v>
+        <v>2100</v>
       </c>
       <c r="I79" t="n">
-        <v>870</v>
+        <v>2100</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>720</v>
+        <v>2100</v>
       </c>
       <c r="L79" t="n">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="M79" t="n">
         <v>2</v>
@@ -9729,145 +9625,145 @@
         <v>2</v>
       </c>
       <c r="O79" t="n">
-        <v>0.06</v>
+        <v>0.074</v>
       </c>
       <c r="P79" t="n">
-        <v>0.06</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ITcs-ME</t>
+          <t>ITn-SI</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1200</v>
+        <v>1260</v>
       </c>
       <c r="C80" t="n">
-        <v>1200</v>
+        <v>1353</v>
       </c>
       <c r="D80" t="n">
-        <v>1200</v>
+        <v>1280</v>
       </c>
       <c r="E80" t="n">
-        <v>1200</v>
+        <v>1241</v>
       </c>
       <c r="F80" t="n">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="G80" t="n">
-        <v>1200</v>
+        <v>1134</v>
       </c>
       <c r="H80" t="n">
-        <v>1200</v>
+        <v>1245</v>
       </c>
       <c r="I80" t="n">
-        <v>1200</v>
+        <v>1094</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ITn-ITs</t>
+          <t>ITsic-MT</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2100</v>
+        <v>450</v>
       </c>
       <c r="C81" t="n">
-        <v>2100</v>
+        <v>450</v>
       </c>
       <c r="D81" t="n">
-        <v>2100</v>
+        <v>450</v>
       </c>
       <c r="E81" t="n">
-        <v>2100</v>
+        <v>450</v>
       </c>
       <c r="F81" t="n">
-        <v>2100</v>
+        <v>450</v>
       </c>
       <c r="G81" t="n">
-        <v>2100</v>
+        <v>450</v>
       </c>
       <c r="H81" t="n">
-        <v>2100</v>
+        <v>450</v>
       </c>
       <c r="I81" t="n">
-        <v>2100</v>
+        <v>450</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ITn-SI</t>
+          <t>LT-LV</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1260</v>
+        <v>2200</v>
       </c>
       <c r="C82" t="n">
-        <v>1353</v>
+        <v>1750</v>
       </c>
       <c r="D82" t="n">
-        <v>1280</v>
+        <v>2200</v>
       </c>
       <c r="E82" t="n">
-        <v>1241</v>
+        <v>1750</v>
       </c>
       <c r="F82" t="n">
-        <v>1220</v>
+        <v>2200</v>
       </c>
       <c r="G82" t="n">
-        <v>1134</v>
+        <v>1750</v>
       </c>
       <c r="H82" t="n">
-        <v>1245</v>
+        <v>2200</v>
       </c>
       <c r="I82" t="n">
-        <v>1094</v>
+        <v>1750</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
@@ -9894,32 +9790,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ITsic-MT</t>
+          <t>LT-PL</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="C83" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="D83" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="E83" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="F83" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="G83" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="H83" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="I83" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="J83" t="b">
         <v>0</v>
@@ -9946,84 +9842,84 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LT-LV</t>
+          <t>LT-SE4</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2200</v>
+        <v>700</v>
       </c>
       <c r="C84" t="n">
-        <v>1750</v>
+        <v>700</v>
       </c>
       <c r="D84" t="n">
-        <v>2200</v>
+        <v>700</v>
       </c>
       <c r="E84" t="n">
-        <v>1750</v>
+        <v>700</v>
       </c>
       <c r="F84" t="n">
-        <v>2200</v>
+        <v>700</v>
       </c>
       <c r="G84" t="n">
-        <v>1750</v>
+        <v>700</v>
       </c>
       <c r="H84" t="n">
-        <v>2200</v>
+        <v>700</v>
       </c>
       <c r="I84" t="n">
-        <v>1750</v>
+        <v>700</v>
       </c>
       <c r="J84" t="b">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LT-PL</t>
+          <t>ME-RS</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>700</v>
+        <v>440</v>
       </c>
       <c r="C85" t="n">
-        <v>700</v>
+        <v>1140</v>
       </c>
       <c r="D85" t="n">
-        <v>700</v>
+        <v>440</v>
       </c>
       <c r="E85" t="n">
-        <v>700</v>
+        <v>1140</v>
       </c>
       <c r="F85" t="n">
-        <v>700</v>
+        <v>440</v>
       </c>
       <c r="G85" t="n">
-        <v>700</v>
+        <v>1140</v>
       </c>
       <c r="H85" t="n">
-        <v>700</v>
+        <v>440</v>
       </c>
       <c r="I85" t="n">
-        <v>700</v>
+        <v>1140</v>
       </c>
       <c r="J85" t="b">
         <v>0</v>
@@ -10050,197 +9946,197 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LT-SE4</t>
+          <t>MK-RS</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="C86" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="D86" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E86" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F86" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G86" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H86" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I86" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J86" t="b">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ME-RS</t>
+          <t>NL-NLll</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>440</v>
+        <v>1800</v>
       </c>
       <c r="C87" t="n">
-        <v>1140</v>
+        <v>2000</v>
       </c>
       <c r="D87" t="n">
-        <v>440</v>
+        <v>1800</v>
       </c>
       <c r="E87" t="n">
-        <v>1140</v>
+        <v>2000</v>
       </c>
       <c r="F87" t="n">
-        <v>440</v>
+        <v>1800</v>
       </c>
       <c r="G87" t="n">
-        <v>1140</v>
+        <v>2000</v>
       </c>
       <c r="H87" t="n">
-        <v>440</v>
+        <v>1800</v>
       </c>
       <c r="I87" t="n">
-        <v>1140</v>
+        <v>2000</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MK-RS</t>
+          <t>NL-NOs</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="C88" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D88" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E88" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F88" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G88" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="H88" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="I88" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="J88" t="b">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NL-NOs</t>
+          <t>NL-UKgb</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="C89" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="D89" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E89" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="F89" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="G89" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="H89" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="I89" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="L89" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="M89" t="n">
         <v>2</v>
@@ -10249,50 +10145,50 @@
         <v>2</v>
       </c>
       <c r="O89" t="n">
-        <v>0.06</v>
+        <v>0.012</v>
       </c>
       <c r="P89" t="n">
-        <v>0.06</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NL-UKgb</t>
+          <t>NLll-UKgb</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="C90" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D90" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="E90" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F90" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="G90" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H90" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="I90" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="L90" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="M90" t="n">
         <v>2</v>
@@ -10301,10 +10197,10 @@
         <v>2</v>
       </c>
       <c r="O90" t="n">
-        <v>0.012</v>
+        <v>0.06</v>
       </c>
       <c r="P90" t="n">
-        <v>0.012</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="91">
@@ -10726,32 +10622,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PL-SK</t>
+          <t>RO-RS</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>894</v>
+        <v>2024</v>
       </c>
       <c r="C99" t="n">
-        <v>880</v>
+        <v>1843</v>
       </c>
       <c r="D99" t="n">
-        <v>894</v>
+        <v>2024</v>
       </c>
       <c r="E99" t="n">
-        <v>880</v>
+        <v>1843</v>
       </c>
       <c r="F99" t="n">
-        <v>894</v>
+        <v>2013</v>
       </c>
       <c r="G99" t="n">
-        <v>880</v>
+        <v>1826</v>
       </c>
       <c r="H99" t="n">
-        <v>894</v>
+        <v>2013</v>
       </c>
       <c r="I99" t="n">
-        <v>880</v>
+        <v>1826</v>
       </c>
       <c r="J99" t="b">
         <v>0</v>
@@ -10778,32 +10674,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RO-RS</t>
+          <t>SE1-SE2</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2024</v>
+        <v>3300</v>
       </c>
       <c r="C100" t="n">
-        <v>1843</v>
+        <v>3300</v>
       </c>
       <c r="D100" t="n">
-        <v>2024</v>
+        <v>3300</v>
       </c>
       <c r="E100" t="n">
-        <v>1843</v>
+        <v>3300</v>
       </c>
       <c r="F100" t="n">
-        <v>2013</v>
+        <v>3300</v>
       </c>
       <c r="G100" t="n">
-        <v>1826</v>
+        <v>3300</v>
       </c>
       <c r="H100" t="n">
-        <v>2013</v>
+        <v>3300</v>
       </c>
       <c r="I100" t="n">
-        <v>1826</v>
+        <v>3300</v>
       </c>
       <c r="J100" t="b">
         <v>0</v>
@@ -10830,32 +10726,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SE1-SE2</t>
+          <t>SE2-SE3</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3300</v>
+        <v>8100</v>
       </c>
       <c r="C101" t="n">
-        <v>3300</v>
+        <v>8100</v>
       </c>
       <c r="D101" t="n">
-        <v>3300</v>
+        <v>8100</v>
       </c>
       <c r="E101" t="n">
-        <v>3300</v>
+        <v>8100</v>
       </c>
       <c r="F101" t="n">
-        <v>3300</v>
+        <v>8100</v>
       </c>
       <c r="G101" t="n">
-        <v>3300</v>
+        <v>8100</v>
       </c>
       <c r="H101" t="n">
-        <v>3300</v>
+        <v>8100</v>
       </c>
       <c r="I101" t="n">
-        <v>3300</v>
+        <v>8100</v>
       </c>
       <c r="J101" t="b">
         <v>0</v>
@@ -10882,93 +10778,93 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SE2-SE3</t>
+          <t>SE3-SE4</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>8100</v>
+        <v>6200</v>
       </c>
       <c r="C102" t="n">
-        <v>8100</v>
+        <v>2800</v>
       </c>
       <c r="D102" t="n">
-        <v>8100</v>
+        <v>6200</v>
       </c>
       <c r="E102" t="n">
-        <v>8100</v>
+        <v>2800</v>
       </c>
       <c r="F102" t="n">
-        <v>8100</v>
+        <v>6200</v>
       </c>
       <c r="G102" t="n">
-        <v>8100</v>
+        <v>2800</v>
       </c>
       <c r="H102" t="n">
-        <v>8100</v>
+        <v>6200</v>
       </c>
       <c r="I102" t="n">
-        <v>8100</v>
+        <v>2800</v>
       </c>
       <c r="J102" t="b">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SE3-SE4</t>
+          <t>UKgb-UKni</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>6200</v>
+        <v>500</v>
       </c>
       <c r="C103" t="n">
-        <v>2800</v>
+        <v>500</v>
       </c>
       <c r="D103" t="n">
-        <v>6200</v>
+        <v>500</v>
       </c>
       <c r="E103" t="n">
-        <v>2800</v>
+        <v>500</v>
       </c>
       <c r="F103" t="n">
-        <v>6200</v>
+        <v>500</v>
       </c>
       <c r="G103" t="n">
-        <v>2800</v>
+        <v>500</v>
       </c>
       <c r="H103" t="n">
-        <v>6200</v>
+        <v>500</v>
       </c>
       <c r="I103" t="n">
-        <v>2800</v>
+        <v>500</v>
       </c>
       <c r="J103" t="b">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="L103" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="M103" t="n">
         <v>2</v>
@@ -10977,61 +10873,9 @@
         <v>2</v>
       </c>
       <c r="O103" t="n">
-        <v>0.01</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P103" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>UKgb-UKni</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>500</v>
-      </c>
-      <c r="C104" t="n">
-        <v>500</v>
-      </c>
-      <c r="D104" t="n">
-        <v>500</v>
-      </c>
-      <c r="E104" t="n">
-        <v>500</v>
-      </c>
-      <c r="F104" t="n">
-        <v>500</v>
-      </c>
-      <c r="G104" t="n">
-        <v>500</v>
-      </c>
-      <c r="H104" t="n">
-        <v>500</v>
-      </c>
-      <c r="I104" t="n">
-        <v>500</v>
-      </c>
-      <c r="J104" t="b">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>500</v>
-      </c>
-      <c r="L104" t="n">
-        <v>500</v>
-      </c>
-      <c r="M104" t="n">
-        <v>2</v>
-      </c>
-      <c r="N104" t="n">
-        <v>2</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="P104" t="n">
         <v>0.08400000000000001</v>
       </c>
     </row>

--- a/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
+++ b/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
@@ -1261,10 +1261,10 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="P15" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="P46" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="47">
@@ -3231,16 +3231,16 @@
         <v>700</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -3340,12 +3340,8 @@
       <c r="N55" t="n">
         <v>2</v>
       </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4531,16 +4527,16 @@
         <v>700</v>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0.1</v>
+        <v>0.035</v>
       </c>
       <c r="P78" t="n">
-        <v>0.1</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="79">
@@ -6349,10 +6345,10 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="P16" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17">
@@ -8117,10 +8113,10 @@
         <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="P50" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="51">
@@ -8325,10 +8321,10 @@
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -8475,16 +8471,16 @@
         <v>700</v>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -8584,12 +8580,8 @@
       <c r="N59" t="n">
         <v>2</v>
       </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9879,16 +9871,16 @@
         <v>700</v>
       </c>
       <c r="M84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0.1</v>
+        <v>0.035</v>
       </c>
       <c r="P84" t="n">
-        <v>0.1</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="85">

--- a/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
+++ b/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,19 @@
       </c>
       <c r="C2" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HVDC</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
+++ b/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
@@ -1170,10 +1170,10 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="14">
@@ -1586,10 +1586,10 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="22">
@@ -1690,10 +1690,10 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="24">
@@ -1742,10 +1742,10 @@
         <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="25">
@@ -1794,10 +1794,10 @@
         <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="26">
@@ -1846,10 +1846,10 @@
         <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="27">
@@ -1950,10 +1950,10 @@
         <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="P28" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="29">
@@ -2158,10 +2158,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="P32" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="33">
@@ -2418,10 +2418,10 @@
         <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="P37" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="38">
@@ -3042,10 +3042,10 @@
         <v>2</v>
       </c>
       <c r="O49" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="P49" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -3762,10 +3762,10 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="14">
@@ -4178,10 +4178,10 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="22">
@@ -4282,10 +4282,10 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="24">
@@ -4334,10 +4334,10 @@
         <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="25">
@@ -4386,10 +4386,10 @@
         <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="26">
@@ -4438,10 +4438,10 @@
         <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="27">
@@ -4542,10 +4542,10 @@
         <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="P28" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="29">
@@ -4750,10 +4750,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="P32" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="33">
@@ -4854,10 +4854,10 @@
         <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
       <c r="P34" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="35">
@@ -5010,10 +5010,10 @@
         <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.074</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P37" t="n">
-        <v>0.074</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -5114,10 +5114,10 @@
         <v>4</v>
       </c>
       <c r="O39" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="P39" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="40">
@@ -5738,10 +5738,10 @@
         <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="P51" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>

--- a/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
+++ b/tests/antares/resources/expected_output_files/links/PEMMDB_LINK.xlsx
@@ -437,10 +437,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
